--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487872_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487872_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0186</v>
+        <v>4.1085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8711</v>
+        <v>1.5793</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1475</v>
+        <v>2.5292</v>
       </c>
       <c r="G2" t="n">
         <v>0.6328</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8919</v>
+        <v>0.198</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3171</v>
+        <v>0.3911</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5747</v>
+        <v>-0.193</v>
       </c>
       <c r="V2" t="n">
         <v>1.4046</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7348</v>
+        <v>2.4128</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8538</v>
+        <v>0.903</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.119</v>
+        <v>1.5098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5951</v>
+        <v>1.8478</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6115</v>
+        <v>-0.3239</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0164</v>
+        <v>2.1717</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4566</v>
+        <v>2.5093</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0525</v>
+        <v>-0.8339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4041</v>
+        <v>3.3432</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8615</v>
+        <v>-0.6615</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5591</v>
+        <v>0.5101</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4206</v>
+        <v>-1.1716</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>2.7055</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0265</v>
+        <v>0.0574</v>
       </c>
       <c r="T3" t="n">
-        <v>3.059</v>
+        <v>0.4749</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0325</v>
+        <v>-0.4175</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0543</v>
+        <v>-0.1168</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5142</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6478</v>
+        <v>2.4094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8951</v>
+        <v>2.0972</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7527</v>
+        <v>0.3123</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0132</v>
@@ -766,13 +766,13 @@
         <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7842</v>
+        <v>-0.0225</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3701</v>
+        <v>-0.1681</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5859</v>
+        <v>0.1456</v>
       </c>
       <c r="V4" t="n">
         <v>1.9883</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1202</v>
+        <v>1.5596</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6746</v>
+        <v>-0.2645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7948</v>
+        <v>1.8241</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0152</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5258</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3972</v>
+        <v>0.8073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1286</v>
+        <v>0.1579</v>
       </c>
       <c r="V5" t="n">
         <v>0.3609</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8314</v>
+        <v>0.4014</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.15</v>
+        <v>0.219</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9813</v>
+        <v>0.1824</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8478</v>
+        <v>-0.6462</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3239</v>
+        <v>-0.0192</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1717</v>
+        <v>-0.627</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5093</v>
+        <v>-0.0867</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8339</v>
+        <v>0.4709</v>
       </c>
       <c r="L6" t="n">
-        <v>3.3432</v>
+        <v>-0.5576</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6615</v>
+        <v>-0.5595</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5101</v>
+        <v>-0.4901</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1716</v>
+        <v>-0.0694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5241</v>
+        <v>0.007</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5780999999999999</v>
+        <v>0.3058</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9459</v>
+        <v>-0.2988</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4997</v>
+        <v>0.3441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6424</v>
+        <v>0.4281</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1427</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1.2647</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1944</v>
+        <v>0.0388</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0633</v>
+        <v>-0.0045</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1675</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2084</v>
+        <v>0.0501</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5963000000000001</v>
+        <v>0.2278</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3879</v>
+        <v>-0.1777</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6462</v>
+        <v>0.5951</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0192</v>
+        <v>1.6115</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.627</v>
+        <v>-1.0164</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0867</v>
+        <v>1.4566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4709</v>
+        <v>1.0525</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5576</v>
+        <v>0.4041</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5595</v>
+        <v>-0.8615</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4901</v>
+        <v>0.5591</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0694</v>
+        <v>-1.4206</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0406</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6028</v>
+        <v>1.3418</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5096000000000001</v>
+        <v>1.4331</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0543</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3659</v>
+        <v>-1.3174</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8731</v>
+        <v>-1.766</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5073</v>
+        <v>0.4486</v>
       </c>
       <c r="G9" t="n">
         <v>-1.041</v>
@@ -1156,13 +1156,13 @@
         <v>0.6244</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1398</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2871</v>
+        <v>0.2284</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5425</v>
+        <v>-2.3764</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2104</v>
+        <v>-2.0443</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3321</v>
@@ -1234,10 +1234,10 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4287</v>
+        <v>0.5948</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4907</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0619</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1843</v>
+        <v>-4.0621</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3039</v>
+        <v>-4.9468</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1196</v>
+        <v>0.8847</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0929</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7411</v>
+        <v>-0.1367</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7763</v>
+        <v>0.1334</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0352</v>
+        <v>-0.2701</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5514</v>
+        <v>3.530000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5459</v>
+        <v>-3.5672</v>
       </c>
       <c r="F12" t="n">
         <v>7.097300000000001</v>
@@ -1357,19 +1357,19 @@
         <v>-4.877400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>3.143899999999999</v>
+        <v>3.1439</v>
       </c>
       <c r="I12" t="n">
         <v>-8.0212</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2022000000000004</v>
+        <v>-0.2021999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>-1.0592</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8572000000000002</v>
+        <v>0.8571999999999997</v>
       </c>
       <c r="M12" t="n">
         <v>-4.6753</v>
@@ -1390,19 +1390,19 @@
         <v>17.6901</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2048</v>
+        <v>3.183600000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0103</v>
+        <v>3.9891</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8050999999999999</v>
+        <v>-0.8052</v>
       </c>
       <c r="V12" t="n">
         <v>1.061399999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>6.173800000000001</v>
+        <v>6.1738</v>
       </c>
       <c r="X12" t="n">
         <v>-5.112299999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9743</v>
+        <v>4.283</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2841</v>
+        <v>3.3913</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6902</v>
+        <v>0.8918</v>
       </c>
       <c r="G13" t="n">
         <v>2.4414</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0915</v>
+        <v>-0.7827</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3047</v>
+        <v>-0.1976</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7867</v>
+        <v>-0.5851</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1844</v>
+        <v>3.8151</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2799</v>
+        <v>1.8903</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0955</v>
+        <v>1.9248</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6344</v>
+        <v>4.3127</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1175</v>
+        <v>0.5204</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7519</v>
+        <v>3.7923</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3565</v>
+        <v>3.7495</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0443</v>
+        <v>-0.1815</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4009</v>
+        <v>3.931</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2779</v>
+        <v>0.5632</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0731</v>
+        <v>0.7019</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.351</v>
+        <v>-0.1388</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0082</v>
+        <v>-0.5195</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2795</v>
+        <v>-0.008</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2713</v>
+        <v>-0.5114</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0943</v>
+        <v>2.2387</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1402</v>
+        <v>-0.6582</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9542</v>
+        <v>2.8969</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3127</v>
+        <v>0.6412</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5204</v>
+        <v>-0.2323</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7923</v>
+        <v>0.8736</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7495</v>
+        <v>-0.714</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1815</v>
+        <v>-1.3712</v>
       </c>
       <c r="L15" t="n">
-        <v>3.931</v>
+        <v>0.6572</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5632</v>
+        <v>1.3552</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7019</v>
+        <v>1.1389</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1388</v>
+        <v>0.2164</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2402</v>
+        <v>0.1406</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7581</v>
+        <v>0.0557</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4821</v>
+        <v>0.0849</v>
       </c>
       <c r="V15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3649</v>
+        <v>1.9524</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4439</v>
+        <v>0.1305</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8088</v>
+        <v>1.8219</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6412</v>
+        <v>3.4735</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2323</v>
+        <v>0.5417</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8736</v>
+        <v>2.9318</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.714</v>
+        <v>1.9182</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3712</v>
+        <v>-0.1195</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6572</v>
+        <v>2.0378</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3552</v>
+        <v>1.5552</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1389</v>
+        <v>0.6612</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2164</v>
+        <v>0.894</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2668</v>
+        <v>0.3332</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2701</v>
+        <v>0.2934</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0032</v>
+        <v>0.0398</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1476</v>
+        <v>1.2183</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2376</v>
+        <v>1.1264</v>
       </c>
       <c r="F17" t="n">
-        <v>1.91</v>
+        <v>0.0919</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4735</v>
+        <v>0.1187</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5417</v>
+        <v>-1.7207</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9318</v>
+        <v>1.8394</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9182</v>
+        <v>-0.3139</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1195</v>
+        <v>-2.1859</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0378</v>
+        <v>1.872</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5552</v>
+        <v>0.4325</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6612</v>
+        <v>0.4652</v>
       </c>
       <c r="O17" t="n">
-        <v>0.894</v>
+        <v>-0.0326</v>
       </c>
       <c r="P17" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5285</v>
+        <v>0.4753</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4005</v>
+        <v>0.1458</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1279</v>
+        <v>0.3295</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8137</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4325</v>
+        <v>1.0374</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4834</v>
+        <v>1.1368</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0509</v>
+        <v>-0.0994</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1187</v>
+        <v>-0.6344</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7207</v>
+        <v>0.1175</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8394</v>
+        <v>-0.7519</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3139</v>
+        <v>-0.3565</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1859</v>
+        <v>0.0443</v>
       </c>
       <c r="L18" t="n">
-        <v>1.872</v>
+        <v>-0.4009</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4325</v>
+        <v>-0.2779</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4652</v>
+        <v>0.0731</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0326</v>
+        <v>-0.351</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3105</v>
+        <v>0.8612</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4972</v>
+        <v>1.1364</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1866</v>
+        <v>-0.2752</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3351</v>
+        <v>1.3975</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3351</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.555</v>
+        <v>-0.5359</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4106</v>
+        <v>0.5178</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9656</v>
+        <v>-1.0537</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5491</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4221</v>
+        <v>-0.403</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1611</v>
+        <v>-0.2492</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3773</v>
+        <v>-3.2599</v>
       </c>
       <c r="E20" t="n">
         <v>-3.7002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3229</v>
+        <v>0.4403</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4521</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4684</v>
+        <v>-0.351</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1422</v>
+        <v>-0.0248</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2876</v>
+        <v>-3.6368</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6287</v>
+        <v>-2.4144</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6589</v>
+        <v>-1.2225</v>
       </c>
       <c r="G21" t="n">
         <v>0.3799</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3792</v>
+        <v>-0.7284</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2395</v>
+        <v>-0.0252</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1397</v>
+        <v>-0.7032</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4152</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.5296</v>
+        <v>-8.949299999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.160299999999999</v>
+        <v>-8.5174</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3693</v>
+        <v>-0.432</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8544</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0967</v>
+        <v>-0.5164</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7581</v>
+        <v>-0.1152</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3385</v>
+        <v>-0.4012</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.551500000000002</v>
+        <v>-1.836999999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.097299999999999</v>
+        <v>-7.097100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5459</v>
+        <v>5.26</v>
       </c>
       <c r="G23" t="n">
         <v>4.8774</v>
@@ -2221,7 +2221,7 @@
         <v>8.0214</v>
       </c>
       <c r="J23" t="n">
-        <v>4.675099999999999</v>
+        <v>4.6751</v>
       </c>
       <c r="K23" t="n">
         <v>-4.2033</v>
@@ -2248,13 +2248,13 @@
         <v>13.5276</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2051</v>
+        <v>-1.4907</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8053000000000001</v>
+        <v>0.8053</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.0103</v>
+        <v>-2.2959</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0614</v>
